--- a/assessment_forms/031_information_systems_concepts_quiz--assessment_forms.xlsx
+++ b/assessment_forms/031_information_systems_concepts_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>information_systems_concept</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>systems_analysis_and_design</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>systems_development</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -607,46 +607,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>systems_thinking</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is information systems?</t>
+          <t>What is systems thinking?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>systems_concepts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is information systems?</t>
+          <t>What are some key information systems concepts?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>key_characteristics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is information systems concepts?</t>
+          <t>What are some key characteristics of information systems?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,23 +676,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>systems_lifecycle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is systems thinking?</t>
+          <t>What is the systems lifecycle?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>systems_architecture</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is systems analysis?</t>
+          <t>What is the systems architecture?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>systems_deployment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is information systems?</t>
+          <t>What is systems deployment?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>systems_maintenance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is systems development?</t>
+          <t>What is systems maintenance?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,39 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>systems_evaluation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is information systems?</t>
+          <t>What is systems evaluation?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What is systems analysis and design?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -825,7 +802,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -850,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>information_systems_concept_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -867,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>information_systems_concept_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -884,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>systems_analysis_and_design_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -901,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>systems_analysis_and_design_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -918,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>systems_development_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -935,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>systems_development_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>systems_thinking_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>systems_thinking_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -986,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>systems_lifecycle_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1003,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>systems_lifecycle_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1020,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>systems_architecture_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1037,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>systems_architecture_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1054,7 +1031,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>systems_deployment_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1071,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>systems_deployment_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1088,7 +1065,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>systems_maintenance_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1105,7 +1082,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>systems_maintenance_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1122,7 +1099,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>systems_evaluation_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1139,7 +1116,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>systems_evaluation_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
